--- a/database_transaksi_bss.xlsx
+++ b/database_transaksi_bss.xlsx
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GS005/IX/2026</t>
+          <t>GS006/IX/2026</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -544,7 +544,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GS JOB02 - GS JOB Sewa Alat</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -553,25 +553,25 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pec</t>
+          <t>rim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CRANE TADANO 70 TON #CR 05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Biaya pengawalan crane tadao</t>
+          <t>Kerta 4A untuk Kantor GS; Polpen untuk kantor</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1000000</v>
+        <v>120000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1000000</v>
+        <v>120000</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -599,10 +599,14 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Kapolsek batui</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t>Agro 88</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>No 02</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>-</t>
@@ -610,14 +614,14 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>[{"Keterangan \/ Nama Barang":"Biaya pengawalan crane tadao","Qty":1.0,"Satuan":"pec","Business Unit":"GS JOB02 - GS JOB Sewa Alat","Peruntukan Alat":"CRANE TADANO 70 TON #CR 05","Nilai DPP (Rp)":1000000.0}]</t>
+          <t>[{"Keterangan \/ Nama Barang":"Kerta 4A untuk Kantor GS","Qty":4.0,"Satuan":"rim","Business Unit":"-","Peruntukan Alat":"-","Nilai DPP (Rp)":50000.0},{"Keterangan \/ Nama Barang":"Polpen untuk kantor","Qty":12.0,"Satuan":"pc","Business Unit":null,"Peruntukan Alat":null,"Nilai DPP (Rp)":70000.0}]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GS006/IX/2026</t>
+          <t>GS005/IX/2026</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -631,7 +635,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GS JOB02 - GS JOB Sewa Alat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -640,25 +644,25 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rim</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CRANE TADANO 70 TON #CR 05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kerta 4A untuk Kantor GS; Polpen untuk kantor</t>
+          <t>Biaya pengawalan crane tadao</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>120000</v>
+        <v>750000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -667,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>120000</v>
+        <v>750000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -686,14 +690,10 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Agro 88</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>No 02</t>
-        </is>
-      </c>
+          <t>Kapolsek batui</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
           <t>-</t>
@@ -701,7 +701,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>[{"Keterangan \/ Nama Barang":"Kerta 4A untuk Kantor GS","Qty":4.0,"Satuan":"rim","Business Unit":"-","Peruntukan Alat":"-","Nilai DPP (Rp)":50000.0},{"Keterangan \/ Nama Barang":"Polpen untuk kantor","Qty":12.0,"Satuan":"pc","Business Unit":null,"Peruntukan Alat":null,"Nilai DPP (Rp)":70000.0}]</t>
+          <t>[{"Keterangan \/ Nama Barang":"Biaya pengawalan crane tadao","Qty":1.0,"Satuan":"Trip","Business Unit":"GS JOB02 - GS JOB Sewa Alat","Peruntukan Alat":"CRANE TADANO 70 TON #CR 05","Nilai DPP (Rp)":750000.0}]</t>
         </is>
       </c>
     </row>

--- a/database_transaksi_bss.xlsx
+++ b/database_transaksi_bss.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,25 +522,32 @@
           <t>Raw_Items</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Catatan Revisi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GS006/IX/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>46266</v>
+          <t>GS005/IX/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kas Keluar (-- Pilih Akun Kas 1110 --)</t>
+          <t>1110.014 - Kas Proyek GS Umum</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GS JOB02 - GS JOB Sewa Alat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -553,25 +556,25 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>rim</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CRANE TADANO 70 TON #CR 05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kerta 4A untuk Kantor GS; Polpen untuk kantor</t>
+          <t>Biaya pengawalan crane tadao</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>120000</v>
+        <v>750000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -580,11 +583,11 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>120000</v>
+        <v>750000</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Menunggu Approval Kepala Bagian Operasional</t>
+          <t>Disetujui Bagian Keuangan (Selesai)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -599,14 +602,10 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Agro 88</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>No 02</t>
-        </is>
-      </c>
+          <t>Kapolsek Batui</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>-</t>
@@ -614,28 +613,31 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>[{"Keterangan \/ Nama Barang":"Kerta 4A untuk Kantor GS","Qty":4.0,"Satuan":"rim","Business Unit":"-","Peruntukan Alat":"-","Nilai DPP (Rp)":50000.0},{"Keterangan \/ Nama Barang":"Polpen untuk kantor","Qty":12.0,"Satuan":"pc","Business Unit":null,"Peruntukan Alat":null,"Nilai DPP (Rp)":70000.0}]</t>
-        </is>
-      </c>
+          <t>[{"Keterangan \/ Nama Barang":"Biaya pengawalan crane tadao","Qty":1.0,"Satuan":"Trip","Business Unit":"GS JOB02 - GS JOB Sewa Alat","Peruntukan Alat":"CRANE TADANO 70 TON #CR 05","Nilai DPP (Rp)":750000.0}]</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GS005/IX/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46266</v>
+          <t>GS006/IX/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kas Keluar (-- Pilih Akun Kas 1110 --)</t>
+          <t>1110.014 - Kas Proyek GS Umum</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GS JOB02 - GS JOB Sewa Alat</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -644,25 +646,25 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>rim</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CRANE TADANO 70 TON #CR 05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Biaya pengawalan crane tadao</t>
+          <t>Kerta 4A untuk Kantor GS; Polpen untuk kantor</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>750000</v>
+        <v>120000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -671,11 +673,11 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>750000</v>
+        <v>120000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Menunggu Approval Kepala Bagian Operasional</t>
+          <t>Ditolak/Revisi oleh Kabag Operasional</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -690,10 +692,14 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Kapolsek batui</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+          <t>Agro 88</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>No 02</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>-</t>
@@ -701,7 +707,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>[{"Keterangan \/ Nama Barang":"Biaya pengawalan crane tadao","Qty":1.0,"Satuan":"Trip","Business Unit":"GS JOB02 - GS JOB Sewa Alat","Peruntukan Alat":"CRANE TADANO 70 TON #CR 05","Nilai DPP (Rp)":750000.0}]</t>
+          <t>[{"Keterangan \/ Nama Barang":"Kerta 4A untuk Kantor GS","Qty":4.0,"Satuan":"rim","Business Unit":"-","Peruntukan Alat":"-","Nilai DPP (Rp)":50000.0},{"Keterangan \/ Nama Barang":"Polpen untuk kantor","Qty":12.0,"Satuan":"pc","Business Unit":null,"Peruntukan Alat":null,"Nilai DPP (Rp)":70000.0}]</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Tolong di beri catatan merek polpen</t>
         </is>
       </c>
     </row>

--- a/database_transaksi_bss.xlsx
+++ b/database_transaksi_bss.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kerta 4A untuk Kantor GS; Polpen untuk kantor</t>
+          <t>Kerta 4A untuk Kantor GS; Polpen untuk kantor Polpen merek pilok</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -677,7 +677,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Ditolak/Revisi oleh Kabag Operasional</t>
+          <t>Disetujui Bagian Keuangan (Selesai)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -707,14 +707,10 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>[{"Keterangan \/ Nama Barang":"Kerta 4A untuk Kantor GS","Qty":4.0,"Satuan":"rim","Business Unit":"-","Peruntukan Alat":"-","Nilai DPP (Rp)":50000.0},{"Keterangan \/ Nama Barang":"Polpen untuk kantor","Qty":12.0,"Satuan":"pc","Business Unit":null,"Peruntukan Alat":null,"Nilai DPP (Rp)":70000.0}]</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Tolong di beri catatan merek polpen</t>
-        </is>
-      </c>
+          <t>[{"Keterangan \/ Nama Barang":"Kerta 4A untuk Kantor GS","Qty":4.0,"Satuan":"rim","Business Unit":"-","Peruntukan Alat":"-","Nilai DPP (Rp)":50000.0},{"Keterangan \/ Nama Barang":"Polpen untuk kantor Polpen merek pilok","Qty":12.0,"Satuan":"pc","Business Unit":null,"Peruntukan Alat":null,"Nilai DPP (Rp)":70000.0}]</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_transaksi_bss.xlsx
+++ b/database_transaksi_bss.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,100 @@
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GS007/IX/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1110.014 - Kas Proyek GS Umum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GS JOB01 - GS JOB Senoro Drilling</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Operasional</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>pc</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Administrasi Keuangan</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ATK Buku Tulis</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Disetujui Bagian Keuangan (Selesai)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Belum Dijurnal</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>elvira sutrisno</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Iyono</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Not 003</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>[{"Keterangan \/ Nama Barang":"ATK Buku Tulis","Qty":1.0,"Satuan":"pc","Business Unit":"GS JOB01 - GS JOB Senoro Drilling","Peruntukan Alat":"Administrasi Keuangan","Nilai DPP (Rp)":200000.0}]</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
